--- a/QA-Assignment/TestCases.xlsx
+++ b/QA-Assignment/TestCases.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9708" firstSheet="5" activeTab="7"/>
+    <workbookView windowWidth="23040" windowHeight="9108" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -6324,8 +6324,8 @@
       <c r="K6" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="L6" s="9" t="s">
-        <v>276</v>
+      <c r="L6" s="5" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
